--- a/outputs_xlsx_solution/test_new1.4-wide-NR-4.xlsx
+++ b/outputs_xlsx_solution/test_new1.4-wide-NR-4.xlsx
@@ -71,6 +71,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -561,7 +567,7 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -581,13 +587,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -607,13 +613,13 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -633,13 +639,19 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
         <v>12</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -659,13 +671,13 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -688,7 +700,7 @@
         <v>11</v>
       </c>
       <c r="N7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -708,13 +720,13 @@
         <v>9</v>
       </c>
       <c r="M8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" t="s">
         <v>11</v>
       </c>
       <c r="O8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -734,13 +746,13 @@
         <v>9</v>
       </c>
       <c r="M9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O9" t="s">
         <v>11</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -760,13 +772,13 @@
         <v>9</v>
       </c>
       <c r="N10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
         <v>11</v>
       </c>
       <c r="P10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -786,13 +798,16 @@
         <v>9</v>
       </c>
       <c r="N11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" t="s">
         <v>12</v>
       </c>
       <c r="P11" t="s">
         <v>11</v>
       </c>
       <c r="Q11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -812,16 +827,16 @@
         <v>9</v>
       </c>
       <c r="N12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="s">
         <v>11</v>
       </c>
       <c r="R12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -841,16 +856,16 @@
         <v>9</v>
       </c>
       <c r="O13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="s">
         <v>11</v>
       </c>
       <c r="R13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -870,13 +885,16 @@
         <v>9</v>
       </c>
       <c r="P14" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" t="s">
         <v>12</v>
       </c>
       <c r="R14" t="s">
         <v>11</v>
       </c>
       <c r="S14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -896,16 +914,16 @@
         <v>9</v>
       </c>
       <c r="P15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S15" t="s">
         <v>11</v>
       </c>
       <c r="T15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -925,16 +943,16 @@
         <v>9</v>
       </c>
       <c r="Q16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S16" t="s">
         <v>11</v>
       </c>
       <c r="T16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -954,13 +972,16 @@
         <v>9</v>
       </c>
       <c r="R17" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" t="s">
         <v>12</v>
       </c>
       <c r="T17" t="s">
         <v>11</v>
       </c>
       <c r="U17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -980,21 +1001,21 @@
         <v>9</v>
       </c>
       <c r="R18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U18" t="s">
         <v>11</v>
       </c>
       <c r="V18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1002,7 +1023,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1010,15 +1031,15 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1026,39 +1047,55 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
         <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
